--- a/src/database/temp_outputs/all_states_surgery_npi_result.xlsx
+++ b/src/database/temp_outputs/all_states_surgery_npi_result.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,29 +541,25 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1154801671000</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1151493808000</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>NPI-1</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1352837665000</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1210105909000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1760491179</t>
+          <t>1427085877</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '35477 KENAI SPUR HWY', 'address_2': 'SUITE 201', 'city': 'SOLDOTNA', 'state': 'AK', 'postal_code': '996697625', 'telephone_number': '907-262-6800', 'fax_number': '907-262-9276'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '203 W PIONEER AVE', 'address_2': 'SUITE 2', 'city': 'HOMER', 'state': 'AK', 'postal_code': '996037527', 'telephone_number': '907-235-3225', 'fax_number': '907-235-3203'}]</t>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '1120 HUFFMAN RD # 587', 'city': 'ANCHORAGE', 'state': 'AK', 'postal_code': '995153516', 'telephone_number': '907-277-1111', 'fax_number': '907-277-1136'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '2841 DEBARR RD', 'address_2': 'STE 46', 'city': 'ANCHORAGE', 'state': 'AK', 'postal_code': '995082932', 'telephone_number': '907-277-1111', 'fax_number': '907-277-1136'}]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -573,12 +569,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[{'code': '208600000X', 'taxonomy_group': '', 'desc': 'Surgery', 'state': 'AK', 'license': '3945', 'primary': True}]</t>
+          <t>[{'code': '208600000X', 'taxonomy_group': '', 'desc': 'Surgery', 'state': 'AK', 'license': '4943', 'primary': True}]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': 'MD6688', 'state': 'AK'}]</t>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': 'MD49431', 'state': 'AK'}]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -593,22 +589,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>GRANT</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>SEARLES</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>M</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>BOLING</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>TODD</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>D.O.</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -623,12 +619,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2006-08-05</t>
+          <t>2006-06-28</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2012-11-13</t>
+          <t>2008-05-06</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -638,7 +634,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>Dr.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -649,20 +645,16 @@
       <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1145908576000</t>
-        </is>
+      <c r="A3" t="n">
+        <v>1145908576000</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>NPI-1</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1701791411000</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1701791411000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -761,29 +753,25 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1160693270000</t>
-        </is>
+      <c r="A4" t="n">
+        <v>1154801671000</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>NPI-1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1183947785000</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1352837665000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1497844617</t>
+          <t>1760491179</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '3268 HOSPITAL DR', 'city': 'JUNEAU', 'state': 'AK', 'postal_code': '998017808', 'telephone_number': '907-586-4126', 'fax_number': '907-586-4134'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '3268 HOSPITAL DR', 'city': 'JUNEAU', 'state': 'AK', 'postal_code': '998017808', 'telephone_number': '907-586-4126', 'fax_number': '907-586-4134'}]</t>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '35477 KENAI SPUR HWY', 'address_2': 'SUITE 201', 'city': 'SOLDOTNA', 'state': 'AK', 'postal_code': '996697625', 'telephone_number': '907-262-6800', 'fax_number': '907-262-9276'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '203 W PIONEER AVE', 'address_2': 'SUITE 2', 'city': 'HOMER', 'state': 'AK', 'postal_code': '996037527', 'telephone_number': '907-235-3225', 'fax_number': '907-235-3203'}]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -793,12 +781,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[{'code': '174400000X', 'taxonomy_group': '', 'desc': 'Specialist', 'state': 'AK', 'license': '282764', 'primary': True}]</t>
+          <t>[{'code': '208600000X', 'taxonomy_group': '', 'desc': 'Surgery', 'state': 'AK', 'license': '3945', 'primary': True}]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': 'MD3105', 'state': 'AK'}]</t>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': 'MD6688', 'state': 'AK'}]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -813,27 +801,27 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>M</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>MILLER</t>
+          <t>BOLING</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ALLEN</t>
+          <t>TODD</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>M.D.</t>
+          <t>D.O.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -843,12 +831,12 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2006-10-12</t>
+          <t>2006-08-05</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2007-07-08</t>
+          <t>2012-11-13</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -869,29 +857,25 @@
       <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1151493808000</t>
-        </is>
+      <c r="A5" t="n">
+        <v>1160693270000</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>NPI-1</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1210105909000</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1183947785000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1427085877</t>
+          <t>1497844617</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '1120 HUFFMAN RD # 587', 'city': 'ANCHORAGE', 'state': 'AK', 'postal_code': '995153516', 'telephone_number': '907-277-1111', 'fax_number': '907-277-1136'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '2841 DEBARR RD', 'address_2': 'STE 46', 'city': 'ANCHORAGE', 'state': 'AK', 'postal_code': '995082932', 'telephone_number': '907-277-1111', 'fax_number': '907-277-1136'}]</t>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '3268 HOSPITAL DR', 'city': 'JUNEAU', 'state': 'AK', 'postal_code': '998017808', 'telephone_number': '907-586-4126', 'fax_number': '907-586-4134'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '3268 HOSPITAL DR', 'city': 'JUNEAU', 'state': 'AK', 'postal_code': '998017808', 'telephone_number': '907-586-4126', 'fax_number': '907-586-4134'}]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -901,12 +885,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[{'code': '208600000X', 'taxonomy_group': '', 'desc': 'Surgery', 'state': 'AK', 'license': '4943', 'primary': True}]</t>
+          <t>[{'code': '174400000X', 'taxonomy_group': '', 'desc': 'Specialist', 'state': 'AK', 'license': '282764', 'primary': True}]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': 'MD49431', 'state': 'AK'}]</t>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': 'MD3105', 'state': 'AK'}]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -921,60 +905,272 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>GRANT</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>SEARLES</t>
+          <t>MILLER</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>ALLEN</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>M.D.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2006-10-12</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2007-07-08</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1145295762000</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1321394362000</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1083678858</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '2925 CHICAGO AVE', 'city': 'MINNEAPOLIS', 'state': 'MN', 'postal_code': '554071321', 'telephone_number': '612-262-5000'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '8675 VALLEY CREEK RD', 'city': 'WOODBURY', 'state': 'MN', 'postal_code': '551252337', 'telephone_number': '651-241-3000'}]</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>[{'code': '207Q00000X', 'taxonomy_group': '', 'desc': 'Family Medicine', 'state': 'MN', 'license': '34583', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '791365600', 'state': 'MN'}]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>GREGORY</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>DUNN</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2006-06-28</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2008-05-06</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2006-04-17</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2011-11-15</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1142612873000</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1326894567000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1184693400</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '9604 SOUTHERN PINES COURT', 'city': 'FT LAUDERDALE', 'state': 'FL', 'postal_code': '333286909'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '9604 SOUTHERN PINES COURT', 'city': 'FT LAUDERDALE', 'state': 'FL', 'postal_code': '333286909', 'telephone_number': '954-423-6778'}]</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>[{'code': '207P00000X', 'taxonomy_group': '', 'desc': 'Emergency Medicine', 'state': 'FL', 'license': 'OS6300', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>[{'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'National Prov Identifier', 'identifier': '1184693400', 'state': 'FL'}, {'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '3707024-00', 'state': 'FL'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'Blue Cross/Blue Shield', 'identifier': '80669', 'state': 'FL'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'Tricare', 'identifier': 'call provider', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>JOHN</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ABT</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>DO, FACEP, FACFE</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2006-03-17</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>2012-01-18</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>Dr.</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/database/temp_outputs/all_states_surgery_npi_result.xlsx
+++ b/src/database/temp_outputs/all_states_surgery_npi_result.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,40 +541,44 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1151493808000</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1132681044000</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>NPI-1</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1210105909000</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1555518179000</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1427085877</t>
+          <t>1225011406</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '1120 HUFFMAN RD # 587', 'city': 'ANCHORAGE', 'state': 'AK', 'postal_code': '995153516', 'telephone_number': '907-277-1111', 'fax_number': '907-277-1136'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '2841 DEBARR RD', 'address_2': 'STE 46', 'city': 'ANCHORAGE', 'state': 'AK', 'postal_code': '995082932', 'telephone_number': '907-277-1111', 'fax_number': '907-277-1136'}]</t>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '3800 PARK NICOLLET BLVD', 'city': 'ST LOUIS PARK', 'state': 'MN', 'postal_code': '554162527', 'telephone_number': '952-993-1190'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '3800 PARK NICOLLET BLVD', 'city': 'ST LOUIS PARK', 'state': 'MN', 'postal_code': '554162527', 'telephone_number': '952-993-1190'}]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '12200 MIDDLE SET RD', 'address_2': '100', 'city': 'EDEN PRAIRIE', 'state': 'MN', 'postal_code': '553445415', 'telephone_number': '952-943-8200', 'fax_number': '952-943-8206'}]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[{'code': '208600000X', 'taxonomy_group': '', 'desc': 'Surgery', 'state': 'AK', 'license': '4943', 'primary': True}]</t>
+          <t>[{'code': '208000000X', 'taxonomy_group': '', 'desc': 'Pediatrics', 'state': 'MN', 'license': '45576', 'primary': True}]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': 'MD49431', 'state': 'AK'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -589,22 +593,18 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>GRANT</t>
+          <t>ERIKA-NELL</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>SEARLES</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+          <t>MALVEY-DORN</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>M.D.,PH.D</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -614,17 +614,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2006-06-28</t>
+          <t>2005-11-22</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2008-05-06</t>
+          <t>2019-04-17</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -637,33 +637,33 @@
           <t>Dr.</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1145908576000</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1161647308000</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>NPI-1</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>1701791411000</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1183947785000</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1689630188</t>
+          <t>1043393838</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '917 TUSCALOOSA AVE SW', 'city': 'BIRMINGHAM', 'state': 'AL', 'postal_code': '352111618', 'telephone_number': '205-780-7150', 'fax_number': '205-783-9326'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '917 TUSCALOOSA AVE SW', 'city': 'BIRMINGHAM', 'state': 'AL', 'postal_code': '352111618', 'telephone_number': '205-780-7150', 'fax_number': '205-783-9326'}]</t>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': 'PO BOX 379', 'city': 'NISSWA', 'state': 'MN', 'postal_code': '564680379', 'telephone_number': '218-963-3311', 'fax_number': '218-963-3313'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '5482 COUNTY ROAD 18', 'city': 'NISSWA', 'state': 'MN', 'postal_code': '56468', 'telephone_number': '218-963-3311', 'fax_number': '218-963-3313'}]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -673,12 +673,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[{'code': '208600000X', 'taxonomy_group': '', 'desc': 'Surgery', 'state': 'AL', 'license': '8477', 'primary': True}]</t>
+          <t>[{'code': '111N00000X', 'taxonomy_group': '', 'desc': 'Chiropractor', 'state': 'MN', 'license': 'DC4116', 'primary': True}]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '10325', 'state': 'AL'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'BC/BS', 'identifier': '51010325', 'state': 'AL'}]</t>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '509112800', 'state': 'MN'}]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -693,22 +693,18 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>JOHN</t>
+          <t>DERREK</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>MATHEWS</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>LOUIS</t>
-        </is>
-      </c>
+          <t>JOHNSON</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>M.D.</t>
+          <t>D.C.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,12 +719,12 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2006-04-24</t>
+          <t>2006-10-23</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2007-07-08</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,40 +734,40 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2023-12-05</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1154801671000</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1153958469000</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>NPI-1</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>1352837665000</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1532529011000</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1760491179</t>
+          <t>1255355103</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '35477 KENAI SPUR HWY', 'address_2': 'SUITE 201', 'city': 'SOLDOTNA', 'state': 'AK', 'postal_code': '996697625', 'telephone_number': '907-262-6800', 'fax_number': '907-262-9276'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '203 W PIONEER AVE', 'address_2': 'SUITE 2', 'city': 'HOMER', 'state': 'AK', 'postal_code': '996037527', 'telephone_number': '907-235-3225', 'fax_number': '907-235-3203'}]</t>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '4855 W ARROWHEAD RD', 'city': 'HERMANTOWN', 'state': 'MN', 'postal_code': '558113936', 'telephone_number': '218-786-3540'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '400 EAST THIRD STREET', 'city': 'DULUTH', 'state': 'MN', 'postal_code': '558051951', 'telephone_number': '218-786-3146', 'fax_number': '218-722-8792'}]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -781,12 +777,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[{'code': '208600000X', 'taxonomy_group': '', 'desc': 'Surgery', 'state': 'AK', 'license': '3945', 'primary': True}]</t>
+          <t>[{'code': '207Q00000X', 'taxonomy_group': '', 'desc': 'Family Medicine', 'state': 'OH', 'license': '35-080256 S', 'primary': False}, {'code': '207Q00000X', 'taxonomy_group': '', 'desc': 'Family Medicine', 'state': 'MN', 'license': '46405', 'primary': True}]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': 'MD6688', 'state': 'AK'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -801,22 +797,22 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>RENEE</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>BOLING</t>
+          <t>SCHLABACH</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>TODD</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>D.O.</t>
+          <t>M.D.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -826,17 +822,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2006-08-05</t>
+          <t>2006-07-26</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2012-11-13</t>
+          <t>2018-07-25</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -844,38 +840,34 @@
           <t>A</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>1160693270000</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1135884647000</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>NPI-1</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>1183947785000</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1183947785000</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1497844617</t>
+          <t>1912984048</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '3268 HOSPITAL DR', 'city': 'JUNEAU', 'state': 'AK', 'postal_code': '998017808', 'telephone_number': '907-586-4126', 'fax_number': '907-586-4134'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '3268 HOSPITAL DR', 'city': 'JUNEAU', 'state': 'AK', 'postal_code': '998017808', 'telephone_number': '907-586-4126', 'fax_number': '907-586-4134'}]</t>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '6465 WAYZATA BLVD', 'address_2': 'SUITE 315', 'city': 'ST LOUIS PARK', 'state': 'MN', 'postal_code': '554261728'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '6490 EXCELSIOR BLVD', 'address_2': 'SUITE W300', 'city': 'ST LOUIS PARK', 'state': 'MN', 'postal_code': '554264705', 'telephone_number': '952-993-3242'}]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -885,12 +877,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[{'code': '174400000X', 'taxonomy_group': '', 'desc': 'Specialist', 'state': 'AK', 'license': '282764', 'primary': True}]</t>
+          <t>[{'code': '207RP1001X', 'taxonomy_group': '', 'desc': 'Internal Medicine, Pulmonary Disease', 'state': 'MN', 'license': '39393', 'primary': True}]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': 'MD3105', 'state': 'AK'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -905,37 +897,29 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>NICOLETTE</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>MILLER</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>ALLEN</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>M.D.</t>
-        </is>
-      </c>
+          <t>MYERS</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2006-10-12</t>
+          <t>2005-12-29</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -961,25 +945,29 @@
       <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>1145295762000</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1156071010000</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>NPI-1</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>1321394362000</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1270585087000</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1083678858</t>
+          <t>1609981885</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '2925 CHICAGO AVE', 'city': 'MINNEAPOLIS', 'state': 'MN', 'postal_code': '554071321', 'telephone_number': '612-262-5000'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '8675 VALLEY CREEK RD', 'city': 'WOODBURY', 'state': 'MN', 'postal_code': '551252337', 'telephone_number': '651-241-3000'}]</t>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '9485 SW 72ND ST', 'address_2': 'SUITE A 195', 'city': 'MIAMI', 'state': 'FL', 'postal_code': '331733242', 'telephone_number': '305-271-9560', 'fax_number': '305-273-8711'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '9485 SW 72ND ST', 'address_2': 'SUITE A 195', 'city': 'MIAMI', 'state': 'FL', 'postal_code': '331733242', 'telephone_number': '305-271-9560', 'fax_number': '305-273-8711'}]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -989,12 +977,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[{'code': '207Q00000X', 'taxonomy_group': '', 'desc': 'Family Medicine', 'state': 'MN', 'license': '34583', 'primary': True}]</t>
+          <t>[{'code': '213E00000X', 'taxonomy_group': '', 'desc': 'Podiatrist', 'state': 'FL', 'license': '1293', 'primary': True}]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '791365600', 'state': 'MN'}]</t>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '041134500', 'state': 'FL'}]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1009,27 +997,23 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>GREGORY</t>
+          <t>LAWRENCE</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>DUNN</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
+          <t>COHN</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>DPM</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1039,12 +1023,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2006-04-17</t>
+          <t>2006-08-20</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2011-11-15</t>
+          <t>2010-04-06</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1054,7 +1038,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>Dr.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,110 +1051,5394 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>1147385887000</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1597340389000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1710937545</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '680 COHASSET RD', 'city': 'CHICO', 'state': 'CA', 'postal_code': '959262213', 'telephone_number': '530-342-4395', 'fax_number': '530-894-2325'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '680 COHASSET RD', 'city': 'CHICO', 'state': 'CA', 'postal_code': '959262213', 'telephone_number': '530-342-4395', 'fax_number': '530-894-2325'}]</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '419 SW 15TH ST', 'city': 'OCALA', 'state': 'FL', 'postal_code': '344710609', 'telephone_number': '352-414-7999', 'fax_number': '352-414-7998'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '1000 SUTTER ST', 'city': 'YUBA CITY', 'state': 'CA', 'postal_code': '959913504', 'telephone_number': '530-673-9420', 'fax_number': '530-673-9451'}]</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>[{'code': '207R00000X', 'taxonomy_group': '', 'desc': 'Internal Medicine', 'state': 'CA', 'license': 'C155513', 'primary': False}, {'code': '207RE0101X', 'taxonomy_group': '', 'desc': 'Internal Medicine, Endocrinology, Diabetes &amp; Metabolism', 'state': 'FL', 'license': 'Me 83396', 'primary': False}, {'code': '207RE0101X', 'taxonomy_group': '', 'desc': 'Internal Medicine, Endocrinology, Diabetes &amp; Metabolism', 'state': 'CA', 'license': 'C155513', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>GOPINATH</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>SUNIL</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2006-05-11</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>2020-08-13</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2020-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1150497086000</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1739292733000</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1588608624</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '7331 COLLEGE PKWY', 'address_2': 'STE 200', 'city': 'FORT MYERS', 'state': 'FL', 'postal_code': '339075524', 'telephone_number': '239-947-4042', 'fax_number': '239-390-9976'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '7331 COLLEGE PKWY', 'address_2': 'STE 200', 'city': 'FORT MYERS', 'state': 'FL', 'postal_code': '339075524', 'telephone_number': '239-947-4042', 'fax_number': '239-390-9976'}]</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>[{'code': '207W00000X', 'taxonomy_group': '', 'desc': 'Ophthalmology', 'state': 'FL', 'license': 'ME82974', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>STEPHEN</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>LAQUIS</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>J.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>M.D.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2006-06-16</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Mr.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1136401451000</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1566257500000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1457339004</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '2665 S MONTE CRISTO WAY', 'city': 'LAS VEGAS', 'state': 'NV', 'postal_code': '891172948', 'telephone_number': '954-649-5739'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '2665 S MONTE CRISTO WAY', 'city': 'LAS VEGAS', 'state': 'NV', 'postal_code': '891172948', 'telephone_number': '954-649-5739', 'fax_number': '954-239-5378'}]</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '1731 E HALLANDALE BEACH BLVD', 'city': 'HALLANDALE BEACH', 'state': 'FL', 'postal_code': '330094656', 'telephone_number': '954-456-9696'}]</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>[{'code': '207P00000X', 'taxonomy_group': '', 'desc': 'Emergency Medicine', 'state': 'FL', 'license': 'ME87540', 'primary': False}, {'code': '207P00000X', 'taxonomy_group': '', 'desc': 'Emergency Medicine', 'state': 'NV', 'license': '16111', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[{'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'Medical License', 'identifier': '16111', 'state': 'NV'}, {'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '267591900', 'state': 'FL'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'BC/BS', 'identifier': '81104', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>[{'endpointType': 'OTHERS', 'endpointTypeDescription': 'Other URL', 'endpoint': 'ccalinescu@hotmail.com', 'endpointDescription': 'email', 'affiliation': 'N', 'use': 'DIRECT', 'useDescription': 'Direct', 'contentType': 'CSV', 'contentTypeDescription': 'CSV', 'country_code': 'US', 'country_name': 'United States', 'address_type': 'DOM', 'address_1': '2665 S Monte Cristo Way', 'city': 'Las Vegas', 'state': 'NV', 'postal_code': '891172948'}]</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>CORNELL</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>CALINESCU</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>V.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2006-01-04</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>2019-08-19</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1148319667000</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1206719894000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1346294337</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '2 COLUMBIA DRIVE', 'address_2': 'SUITE: A-327', 'city': 'TAMPA', 'state': 'FL', 'postal_code': '33606', 'telephone_number': '813-844-4434', 'fax_number': '813-844-8458'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '2 COLUMBIA DR', 'address_2': 'SUITE A327', 'city': 'TAMPA', 'state': 'FL', 'postal_code': '336063508', 'telephone_number': '813-844-4396', 'fax_number': '813-844-4972'}]</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>[{'code': '207L00000X', 'taxonomy_group': '', 'desc': 'Anesthesiology', 'state': 'FL', 'license': 'ME73281', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '252098200', 'state': 'FL'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'DOL ACS (FECA) W/C', 'identifier': '300804500', 'state': 'FL'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'FL BCBS Number', 'identifier': '41455', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>EMMANUEL</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>ROLDAN</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>DINDO UBAS</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2006-05-22</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2008-03-28</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>1142612873000</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>NPI-1</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>1326894567000</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>1184693400</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '9604 SOUTHERN PINES COURT', 'city': 'FT LAUDERDALE', 'state': 'FL', 'postal_code': '333286909'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '9604 SOUTHERN PINES COURT', 'city': 'FT LAUDERDALE', 'state': 'FL', 'postal_code': '333286909', 'telephone_number': '954-423-6778'}]</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>[{'code': '207P00000X', 'taxonomy_group': '', 'desc': 'Emergency Medicine', 'state': 'FL', 'license': 'OS6300', 'primary': True}]</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>[{'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'National Prov Identifier', 'identifier': '1184693400', 'state': 'FL'}, {'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '3707024-00', 'state': 'FL'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'Blue Cross/Blue Shield', 'identifier': '80669', 'state': 'FL'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'Tricare', 'identifier': 'call provider', 'state': 'FL'}]</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>JOHN</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>ABT</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>L.</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>DO, FACEP, FACFE</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>2006-03-17</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>2012-01-18</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Dr.</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1159926690000</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1555435023000</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1356436786</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '7460 SW 64TH ST', 'city': 'SOUTH MIAMI', 'state': 'FL', 'postal_code': '331432802', 'telephone_number': '305-691-7515', 'fax_number': '305-666-6211'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '7460 SW 64TH ST', 'city': 'SOUTH MIAMI', 'state': 'FL', 'postal_code': '331432802', 'telephone_number': '305-443-0540', 'fax_number': '305-443-0620'}]</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>[{'code': '207Q00000X', 'taxonomy_group': '', 'desc': 'Family Medicine', 'state': 'FL', 'license': 'ME68741', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '378210700', 'state': 'FL'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'Cigna', 'identifier': '5190726', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>HUMBERTO</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>FERNANDEZ-MIRO</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2006-10-03</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2019-04-16</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1149513713000</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1560965706000</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1497794739</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '1055 SAXON BLVD.,', 'address_2': 'FLORIDA HOSPITAL FISH MEMORIAL', 'city': 'ORANGE CITY', 'state': 'FL', 'postal_code': '32763', 'telephone_number': '386-917-5434', 'fax_number': '386-917-5101'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '397 CADDIE DR', 'city': 'DEBARY', 'state': 'FL', 'postal_code': '327134514', 'telephone_number': '386-917-0811', 'fax_number': '386-917-0812'}]</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>[{'code': '207P00000X', 'taxonomy_group': '', 'desc': 'Emergency Medicine', 'state': 'FL', 'license': 'ME51146', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[{'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'Blue Cross of Florida', 'identifier': '04618', 'state': 'FL'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'Amerigroup', 'identifier': '221871', 'state': 'FL'}, {'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '257134000', 'state': 'FL'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'Railroad Medicare', 'identifier': 'P30090443', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>WAYNE</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>BARRY</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2006-06-05</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1142346029000</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1643378643000</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1508834771</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '7300 BRYAN DAIRY RD', 'address_2': 'ANESTHESIA DEPT', 'city': 'LARGO', 'state': 'FL', 'postal_code': '337771534', 'telephone_number': '727-451-6780', 'fax_number': '770-237-1124'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': 'PO BOX 3978', 'city': 'SEMINOLE', 'state': 'FL', 'postal_code': '337753978', 'telephone_number': '770-237-1561', 'fax_number': '770-237-1124'}]</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>[{'code': '367500000X', 'taxonomy_group': '', 'desc': 'Nurse Anesthetist, Certified Registered', 'state': 'FL', 'license': 'RN2122282', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[{'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'RN License #', 'identifier': 'RN2122282', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>[{'type': 'Former Name', 'code': '1', 'credential': 'CRNA', 'first_name': 'KATHRYN', 'last_name': 'ANDOLINA'}]</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>KATHRYN</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>VANDOLAH</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ROGERS</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>CRNA</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2006-03-14</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2022-01-28</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2022-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1127427494000</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1183947785000</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1063408201</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '12400 101ST ST', 'city': 'LARGO', 'state': 'FL', 'postal_code': '337731934', 'telephone_number': '727-581-5948'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '2 COLUMBIA DR', 'address_2': 'SUITE A327', 'city': 'TAMPA', 'state': 'FL', 'postal_code': '336063508', 'telephone_number': '813-844-4434', 'fax_number': '813-844-4467'}]</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>[{'code': '367500000X', 'taxonomy_group': '', 'desc': 'Nurse Anesthetist, Certified Registered', 'state': 'FL', 'license': 'ARNP 2129302', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '305112900', 'state': 'FL'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'FL BCBS Provider #', 'identifier': 'G3160', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>PATRICK</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>MCCABE</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>WILLIAM ED</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>CRNA</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2005-09-22</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2007-07-08</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1135201997000</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1379532555000</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1831175702</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '3641 S MIAMI AVE', 'city': 'MIAMI', 'state': 'FL', 'postal_code': '331334205', 'telephone_number': '305-854-0302', 'fax_number': '305-854-0308'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '3661 S MIAMI AVE', 'address_2': 'SUITE 107', 'city': 'MIAMI', 'state': 'FL', 'postal_code': '331334236', 'telephone_number': '305-854-0302', 'fax_number': '305-854-0308'}]</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>[{'code': '207L00000X', 'taxonomy_group': '', 'desc': 'Anesthesiology', 'state': 'FL', 'license': 'ME40842', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '062295800', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>FRANCISCO</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>ALVAREZ-GIL</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>M.D.</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2005-12-21</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2013-09-18</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1149155766000</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1265045879000</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1467499285</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '4080 SW 84TH AVE', 'address_2': 'STE D', 'city': 'MIAMI', 'state': 'FL', 'postal_code': '331554201', 'telephone_number': '305-223-1140', 'fax_number': '305-223-1174'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '4080 SW 84TH AVE', 'address_2': 'STE D', 'city': 'MIAMI', 'state': 'FL', 'postal_code': '331554201', 'telephone_number': '305-223-1140', 'fax_number': '305-223-1174'}]</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>[{'code': '207Q00000X', 'taxonomy_group': '', 'desc': 'Family Medicine', 'state': 'FL', 'license': 'ME83255', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '262741800', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>SANTANDER</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>LUIS</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2006-06-01</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2010-02-01</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1143473385000</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1425430373000</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1518927193</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '8850 SW 43RD TER', 'city': 'MIAMI', 'state': 'FL', 'postal_code': '331655332', 'telephone_number': '305-552-7145'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '9333 SW 152ND ST', 'city': 'PALMETTO BAY', 'state': 'FL', 'postal_code': '331571778', 'telephone_number': '305-256-5001'}]</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>[{'code': '207P00000X', 'taxonomy_group': '', 'desc': 'Emergency Medicine', 'state': 'FL', 'license': 'ME0087672', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '268074200', 'state': 'FL'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'BCBS', 'identifier': '81764', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ERICK</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>ANDREU</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2006-03-27</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2015-03-03</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1141243434000</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1332218692000</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1881661684</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '2225 N UNIVERSITY DR', 'city': 'PEMBROKE PINES', 'state': 'FL', 'postal_code': '330243611', 'telephone_number': '954-962-6200', 'fax_number': '954-962-5495'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '3016 NE 210TH ST', 'city': 'MIAMI', 'state': 'FL', 'postal_code': '331803661', 'telephone_number': '305-494-3555', 'fax_number': '954-962-5495'}]</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>[{'code': '1041C0700X', 'taxonomy_group': '', 'desc': 'Social Worker, Clinical', 'state': 'FL', 'license': 'SW5767', 'primary': True}, {'code': '103TA0400X', 'taxonomy_group': '', 'desc': 'Psychologist, Addiction (Substance Use Disorder)', 'state': 'FL', 'license': 'SAP80608', 'primary': False}]</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[{'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'Medicare PTAN', 'identifier': 'E3800B', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>FRONA</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>ISRAEL</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>LCSW, DCFC, SAP</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2006-03-01</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>2012-03-20</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Ms.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1164987823000</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1183947785000</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1225106081</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '21275 OLEAN BLVD', 'city': 'PORT CHARLOTTE', 'state': 'FL', 'postal_code': '339526704', 'telephone_number': '941-624-5559', 'fax_number': '941-624-3777'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '21275 OLEAN BLVD', 'city': 'PORT CHARLOTTE', 'state': 'FL', 'postal_code': '339526704', 'telephone_number': '941-624-5559', 'fax_number': '941-624-3777'}]</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>[{'code': '367500000X', 'taxonomy_group': '', 'desc': 'Nurse Anesthetist, Certified Registered', 'state': 'FL', 'license': 'ARNP 1580382', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[{'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'TAX ID', 'identifier': '650131879', 'state': None}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'BS PROVIDER #', 'identifier': 'G0113', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>MICHAEL</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>BASKIND</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>CRNA</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2006-12-01</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>2007-07-08</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1146750182000</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1348063015000</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1821046079</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '5961 SW 81ST ST', 'city': 'MIAMI', 'state': 'FL', 'postal_code': '331438119', 'telephone_number': '786-412-2156'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '2 W DIXIE HWY', 'address_2': 'AMO CLINIC', 'city': 'DANIA BEACH', 'state': 'FL', 'postal_code': '330044312', 'telephone_number': '786-412-2156'}]</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>[{'code': '174400000X', 'taxonomy_group': '', 'desc': 'Specialist', 'state': 'FL', 'license': 'ME65508', 'primary': True}, {'code': '2083P0500X', 'taxonomy_group': '', 'desc': 'Preventive Medicine, Preventive Medicine/Occupational Environmental Medicine', 'state': 'FL', 'license': 'ME65508', 'primary': False}, {'code': '208D00000X', 'taxonomy_group': '', 'desc': 'General Practice', 'state': 'FL', 'license': 'ME 65508', 'primary': False}]</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ALVARO</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>OCAMPO</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>MD, MPH</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2006-05-04</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>2012-09-19</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1159824546000</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1183947785000</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1740373406</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '2500 SW 107TH AVENUE # 36', 'city': 'MIAMI', 'state': 'FL', 'postal_code': '33165', 'telephone_number': '305-225-2800', 'fax_number': '305-225-1118'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '2500 SW 107TH AVENUE # 36', 'city': 'MIAMI', 'state': 'FL', 'postal_code': '33165', 'telephone_number': '305-225-2800', 'fax_number': '305-225-1118'}]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>[{'code': '207VG0400X', 'taxonomy_group': '', 'desc': 'Obstetrics &amp; Gynecology, Gynecology', 'state': 'FL', 'license': '45171', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '069825300', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>OFILIO</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>ARGUELLO</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>M.D.</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2006-10-02</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>2007-07-08</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1143644905000</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1663261873000</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1669433801</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '2700 RIVERSIDE AVE STE 2', 'city': 'JACKSONVILLE', 'state': 'FL', 'postal_code': '322058233', 'telephone_number': '904-264-8801', 'fax_number': '904-621-0566'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '705 WELLS RD STE 300', 'city': 'ORANGE PARK', 'state': 'FL', 'postal_code': '320732982', 'telephone_number': '904-282-6331', 'fax_number': '904-619-1080'}]</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>[{'code': '207L00000X', 'taxonomy_group': '', 'desc': 'Anesthesiology', 'state': 'FL', 'license': 'ME69375', 'primary': False}, {'code': '207LP2900X', 'taxonomy_group': '', 'desc': 'Anesthesiology, Pain Medicine', 'state': 'FL', 'license': 'ME69375', 'primary': False}, {'code': '208VP0014X', 'taxonomy_group': '', 'desc': 'Pain Medicine, Interventional Pain Medicine', 'state': 'FL', 'license': 'ME69375', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '2649501-00', 'state': 'FL'}, {'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '614436071A', 'state': 'GA'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'Railroad Medicare', 'identifier': 'P00071130', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>TIMOTHY</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>STERNBERG</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>LAMON</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>M.D., D.M.D.</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>2006-03-29</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1158785908000</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1348150195000</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1689772881</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '3505 S ORLANDO DR', 'city': 'SANFORD', 'state': 'FL', 'postal_code': '327735609', 'telephone_number': '407-324-8222', 'fax_number': '407-682-4376'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '3505 S ORLANDO DR', 'city': 'SANFORD', 'state': 'FL', 'postal_code': '327735609', 'telephone_number': '407-324-8222', 'fax_number': '407-682-4376'}]</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>[{'code': '111N00000X', 'taxonomy_group': '', 'desc': 'Chiropractor', 'state': 'FL', 'license': 'CH7803', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[{'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'Tax Identification', 'identifier': '20-8240320', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>MATTHEW</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>DEMETREE</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>CHARLES</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>2006-09-20</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>2012-09-20</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1131729204000</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1396625130000</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1831170240</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '2320 S SEACREST BLVD', 'address_2': 'SUITE 200', 'city': 'BOYNTON BEACH', 'state': 'FL', 'postal_code': '334356517', 'telephone_number': '561-374-9932', 'fax_number': '561-374-9946'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '2320 S SEACREST BLVD', 'address_2': 'SUITE 200', 'city': 'BOYNTON BEACH', 'state': 'FL', 'postal_code': '334356517', 'telephone_number': '561-374-9932', 'fax_number': '561-374-9946'}]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>[{'code': '2084N0400X', 'taxonomy_group': '', 'desc': 'Psychiatry &amp; Neurology, Neurology', 'state': 'FL', 'license': 'ME 0084428', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '271594500', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>TIRADO</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2005-11-11</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>2014-04-04</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Mr.</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1128786772000</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1670869051000</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1417945098</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '5555 PONCE DE LEON BLVD', 'city': 'CORAL GABLES', 'state': 'FL', 'postal_code': '331462513', 'telephone_number': '305-284-3333', 'fax_number': '305-243-2738'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '5555 PONCE DE LEON BLVD', 'city': 'CORAL GABLES', 'state': 'FL', 'postal_code': '331462513', 'telephone_number': '305-284-3333', 'fax_number': '305-243-2738'}]</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>[{'code': '207R00000X', 'taxonomy_group': '', 'desc': 'Internal Medicine', 'state': 'FL', 'license': 'ME56983', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>AVELINO</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>CARIDE</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>RUBEN</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>M.D.</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>2005-10-08</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>2022-12-12</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2022-12-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1143508838000</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1666812896000</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1346200797</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '7400 SW 87TH AVE STE 260', 'city': 'MIAMI', 'state': 'FL', 'postal_code': '331735458', 'telephone_number': '786-595-8040'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': 'PO BOX 198054', 'city': 'ATLANTA', 'state': 'GA', 'postal_code': '303843144', 'telephone_number': '786-594-6880'}]</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>[{'code': '363L00000X', 'taxonomy_group': '', 'desc': 'Nurse Practitioner', 'state': 'FL', 'license': 'ARNP2565872', 'primary': False}, {'code': '363LF0000X', 'taxonomy_group': '', 'desc': 'Nurse Practitioner, Family', 'state': 'FL', 'license': 'ARNP2565872', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>[{'endpointType': 'DIRECT', 'endpointTypeDescription': 'Direct Messaging Address', 'endpoint': 'barbarace@cerner.directbaptisthealth.com', 'affiliation': 'N', 'useDescription': '', 'contentTypeDescription': '', 'country_code': 'US', 'country_name': 'United States', 'address_type': 'DOM', 'address_1': '8900 N Kendall Dr', 'city': 'Miami', 'state': 'FL', 'postal_code': '331762118'}]</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>BARBARA</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>CELEIRO</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>MARIA</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>ARNP</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2006-03-27</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Ms.</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1132337437000</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1344020540000</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1356323810</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '2264 CORAL WAY', 'city': 'CORAL GABLES', 'state': 'FL', 'postal_code': '331453509', 'telephone_number': '305-854-0736', 'fax_number': '305-490-0754'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '2264 CORAL WAY', 'city': 'CORAL GABLES', 'state': 'FL', 'postal_code': '331453509', 'telephone_number': '305-854-0736', 'fax_number': '305-490-0754'}]</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>[{'code': '152W00000X', 'taxonomy_group': '', 'desc': 'Optometrist', 'state': 'FL', 'license': 'op2796', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '620085100', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>MARIA</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>OD,PA</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>2005-11-18</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>2012-08-03</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1175362345000</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1535808332000</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1679693683</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '4760 EAST BAY DR SUITE D', 'city': 'CLEARWATER', 'state': 'FL', 'postal_code': '337641814', 'telephone_number': '727-481-1694', 'fax_number': '727-474-4985'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '2007 DODGE ST', 'city': 'CLEARWATER', 'state': 'FL', 'postal_code': '337601814', 'telephone_number': '727-481-1694', 'fax_number': '727-535-5856'}]</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '2007 DODGE ST', 'city': 'CLEARWATER', 'state': 'FL', 'postal_code': '337601814', 'telephone_number': '727-481-1694', 'fax_number': '727-535-5856'}]</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>[{'code': '225100000X', 'taxonomy_group': '', 'desc': 'Physical Therapist', 'state': 'FL', 'license': 'PT0012196', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '887450600', 'state': 'FL'}, {'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '887450696', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>KATHERYN</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>AMPON</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>2007-03-31</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>2018-09-01</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1120573019000</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1750437870000</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1831196922</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '6315 AMBERWOOD DR', 'city': 'BOCA RATON', 'state': 'FL', 'postal_code': '334333737', 'telephone_number': '216-255-5735', 'fax_number': '216-255-5701'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '23625 COMMERCE PARK', 'address_2': '#204', 'city': 'BEACHWOOD', 'state': 'OH', 'postal_code': '441225845', 'telephone_number': '216-255-5700', 'fax_number': '216-255-5701'}]</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '2041 GEORGIA AVE NW # 1R84', 'city': 'WASHINGTON', 'state': 'DC', 'postal_code': '200603737', 'telephone_number': '202-865-3610'}]</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>[{'code': '2085R0202X', 'taxonomy_group': '', 'desc': 'Radiology, Diagnostic Radiology', 'state': 'NY', 'license': '162764-1', 'primary': False}, {'code': '2085R0202X', 'taxonomy_group': '', 'desc': 'Radiology, Diagnostic Radiology', 'state': 'DC', 'license': 'MD037052', 'primary': False}, {'code': '2085R0202X', 'taxonomy_group': '', 'desc': 'Radiology, Diagnostic Radiology', 'state': 'FL', 'license': 'ME60884', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>[{'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'BCBS', 'identifier': '$$$$$$$$$', 'state': 'LA'}, {'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '00898531', 'state': 'NY'}, {'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '1537748', 'state': 'LA'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'BCBS', 'identifier': '17738', 'state': 'FL'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'TRICARE Prime', 'identifier': '1831196922', 'state': None}, {'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '194202', 'state': 'SC'}, {'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '2771175', 'state': 'OH'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'RR', 'identifier': '300100047', 'state': None}, {'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '376437100', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>FREDERICK</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>LAUFER</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>2005-07-05</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1147952183000</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1746549112000</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1518910918</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '1205 THRUSH AVE', 'city': 'MIAMI SPRINGS', 'state': 'FL', 'postal_code': '331663152', 'telephone_number': '305-450-6360'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '1490 W 49TH PL STE 507', 'city': 'HIALEAH', 'state': 'FL', 'postal_code': '330123190', 'telephone_number': '281-989-0632'}]</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>[{'code': '208D00000X', 'taxonomy_group': '', 'desc': 'General Practice', 'state': 'FL', 'license': 'ME89767', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>RAMON</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>SASTRE</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>2006-05-18</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sr.</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1120573014000</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1437246213000</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1013914100</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '3700 PARK EAST DR', 'address_2': 'SUIT 300', 'city': 'BEACHWOOD', 'state': 'OH', 'postal_code': '441224399', 'telephone_number': '855-292-1401', 'fax_number': '866-396-8340'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '3700 PARK EAST DR', 'address_2': 'SUITE 300', 'city': 'BEACHWOOD', 'state': 'OH', 'postal_code': '441224399', 'telephone_number': '855-292-1401', 'fax_number': '866-396-8340'}]</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>[{'code': '2085R0202X', 'taxonomy_group': '', 'desc': 'Radiology, Diagnostic Radiology', 'state': 'FL', 'license': 'ME75351', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '048775300', 'state': 'DC'}, {'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '1013914100', 'state': 'CA'}, {'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '102338070', 'state': 'PA'}, {'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '254634500', 'state': 'FL'}, {'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '262433800', 'state': 'FL'}, {'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '2761425', 'state': 'OH'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'RRNUM', 'identifier': '300138468', 'state': None}, {'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '323208500', 'state': 'MD'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'BCBS', 'identifier': '43401', 'state': None}, {'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '7100091260', 'state': 'KY'}, {'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '808324000', 'state': 'ID'}, {'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': 'Q75351', 'state': 'SC'}]</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>[{'type': 'Former Name', 'code': '1', 'credential': 'M.D.', 'first_name': 'BEATRIX', 'last_name': 'OUICKERT', 'middle_name': 'DAGMAR', 'prefix': '--', 'suffix': '--'}]</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>BEATRIX</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>ARAIZA</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>DAGMAR</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>M.D.</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>2005-07-05</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>2015-07-18</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1156404532000</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1340989373000</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1619084902</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '1490 WHITMAN DR', 'city': 'MELBOURNE', 'state': 'FL', 'postal_code': '329048749', 'telephone_number': '321-557-2562', 'fax_number': '321-327-2102'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '1490 WHITMAN DR', 'city': 'MELBOURNE', 'state': 'FL', 'postal_code': '329048749', 'telephone_number': '321-557-2562', 'fax_number': '321-327-2102'}]</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>[{'code': '225X00000X', 'taxonomy_group': '', 'desc': 'Occupational Therapist', 'state': 'FL', 'license': 'ot6630', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>WANDA</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>LUNDEN</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>OTR</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>2006-08-24</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>2012-06-29</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Ms.</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1157038051000</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1183947785000</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1336251404</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '300 JEFFORDS ST', 'address_2': 'SUITE B', 'city': 'CLEARWATER', 'state': 'FL', 'postal_code': '337563810', 'telephone_number': '727-441-1524', 'fax_number': '727-443-4206'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '300 PINELLAS ST', 'city': 'CLEARWATER', 'state': 'FL', 'postal_code': '337563804', 'telephone_number': '727-462-7000'}]</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>[{'code': '367500000X', 'taxonomy_group': '', 'desc': 'Nurse Anesthetist, Certified Registered', 'state': 'FL', 'license': 'ARNP1404392', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '300818500', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>BARBARA</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>BRYANT</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>CRNA</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>2006-08-31</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>2007-07-08</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1146871924000</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1322690329000</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1578511861</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '3505 PROGRESS LN', 'city': 'SAINT CLOUD', 'state': 'FL', 'postal_code': '347696519', 'telephone_number': '407-891-8044', 'fax_number': '407-891-8016'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '3505 PROGRESS LN', 'city': 'SAINT CLOUD', 'state': 'FL', 'postal_code': '347696519', 'telephone_number': '407-891-8044', 'fax_number': '407-891-8016'}]</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>[{'code': '207R00000X', 'taxonomy_group': '', 'desc': 'Internal Medicine', 'state': 'FL', 'license': 'ME88379', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '269413100', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>HIZKIL</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>2006-05-05</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>2011-11-30</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1123853143000</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1249936585000</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1386646008</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '1921 WALDEMERE ST', 'address_2': 'SUITE 809', 'city': 'SARASOTA', 'state': 'FL', 'postal_code': '342392913', 'telephone_number': '941-955-1960', 'fax_number': '941-955-1242'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '1921 WALDEMERE ST', 'address_2': 'SUITE 809', 'city': 'SARASOTA', 'state': 'FL', 'postal_code': '342392913', 'telephone_number': '941-955-1960', 'fax_number': '941-955-1242'}]</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>[{'code': '207T00000X', 'taxonomy_group': '', 'desc': 'Neurological Surgery', 'state': 'FL', 'license': 'ME72208', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>SCHUMACHER</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>MATTHEW</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>2005-08-12</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>2009-08-10</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1160761196000</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1743527751000</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1134219967</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '240 N WICKHAM RD STE 309', 'city': 'MELBOURNE', 'state': 'FL', 'postal_code': '329358661', 'telephone_number': '321-752-1630', 'fax_number': '321-690-6578'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '240 N WICKHAM RD STE 309', 'city': 'MELBOURNE', 'state': 'FL', 'postal_code': '329358661', 'telephone_number': '321-752-1630', 'fax_number': '321-690-6578'}]</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '8095 SPYGLASS HILL RD', 'address_2': 'SUITE 104', 'city': 'VIERA', 'state': 'FL', 'postal_code': '329408290', 'telephone_number': '321-576-9030', 'fax_number': '321-576-9031'}]</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>[{'code': '207RG0100X', 'taxonomy_group': '', 'desc': 'Internal Medicine, Gastroenterology', 'state': 'FL', 'license': 'ME49690', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '000594600', 'state': 'FL'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'MEDICARE', 'identifier': '07559A', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ROBERT</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>BARBATI</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>2006-10-13</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1134674054000</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1573155617000</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1700862414</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '5810 SW 16TH ST', 'city': 'MIAMI', 'state': 'FL', 'postal_code': '331552105', 'telephone_number': '305-261-8127', 'fax_number': '786-353-2163'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '5810 SW 16TH ST', 'city': 'MIAMI', 'state': 'FL', 'postal_code': '331552105', 'telephone_number': '305-261-8127', 'fax_number': '786-353-2163'}]</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>[{'code': '208D00000X', 'taxonomy_group': '', 'desc': 'General Practice', 'state': 'FL', 'license': 'ME68564', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>HECTOR</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>LABRADA</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>M.D.</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2005-12-15</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>2019-11-07</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1138297409000</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1260290347000</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1851361273</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '4400 BAYOU BLVD', 'address_2': 'BUILDING 51', 'city': 'PENSACOLA', 'state': 'FL', 'postal_code': '325032673', 'telephone_number': '850-484-8344', 'fax_number': '850-484-2875'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '4400 BAYOU BLVD', 'address_2': 'BUILDING 51', 'city': 'PENSACOLA', 'state': 'FL', 'postal_code': '325032673', 'telephone_number': '850-484-8344', 'fax_number': '850-484-2875'}]</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>[{'code': '103T00000X', 'taxonomy_group': '', 'desc': 'Psychologist', 'state': 'FL', 'license': 'PY2286', 'primary': True}, {'code': '106H00000X', 'taxonomy_group': '', 'desc': 'Marriage &amp; Family Therapist', 'state': 'FL', 'license': 'MT900', 'primary': False}]</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>[{'type': 'Other Name', 'code': '5', 'credential': 'Ph.D.', 'first_name': 'STEVE', 'last_name': 'HIRSCHORN', 'prefix': 'Dr.', 'suffix': '--'}]</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>STEPHEN</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>HIRSCHORN</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Ph.D.</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2006-01-26</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>2009-12-08</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1129472594000</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1258988108000</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1487643128</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '1110 SW 152ND TER', 'city': 'PEMBROKE PINES', 'state': 'FL', 'postal_code': '330272206', 'telephone_number': '954-450-2127', 'fax_number': '954-450-0124'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '1110 SW 152ND TER', 'city': 'PEMBROKE PINES', 'state': 'FL', 'postal_code': '330272206', 'telephone_number': '954-450-2127', 'fax_number': '954-450-0124'}]</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>[{'code': '367500000X', 'taxonomy_group': '', 'desc': 'Nurse Anesthetist, Certified Registered', 'state': 'FL', 'license': '907042', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ELLEN</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>REY</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>CRNA</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2005-10-16</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2009-11-23</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Ms.</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1153171418000</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1622214637000</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1730107103</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '4800 BELFORT RD', 'city': 'JACKSONVILLE', 'state': 'FL', 'postal_code': '322566004', 'telephone_number': '904-398-3262', 'fax_number': '904-265-4807'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '7720 US HIGHWAY 98 W STE 140', 'city': 'MIRAMAR BEACH', 'state': 'FL', 'postal_code': '325507231', 'telephone_number': '904-398-7205', 'fax_number': '904-396-4047'}]</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>[{'code': '207RG0100X', 'taxonomy_group': '', 'desc': 'Internal Medicine, Gastroenterology', 'state': 'FL', 'license': 'ME59582', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>[{'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'BCBS', 'identifier': '12165', 'state': 'FL'}, {'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '276771600', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>STEVEN</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>HARVEY</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>M.D.</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2006-07-17</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>2021-05-28</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2021-05-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1151549777000</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1209490359000</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1275561466</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '8240 SW 185TH TER', 'city': 'CUTLER BAY', 'state': 'FL', 'postal_code': '331577329', 'telephone_number': '305-259-6433', 'fax_number': '305-251-5978'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '8240 SW 185TH TER', 'city': 'MIAMI', 'state': 'FL', 'postal_code': '331577329', 'telephone_number': '305-259-6433'}]</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>[{'code': '103T00000X', 'taxonomy_group': '', 'desc': 'Psychologist', 'state': 'FL', 'license': 'ME0004754', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>[{'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'Neighborhood Health', 'identifier': '033137', 'state': 'FL'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'Avmed', 'identifier': '267440', 'state': 'FL'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'Blue Cross &amp; Blue Shield', 'identifier': '54341', 'state': 'FL'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'Railroad Medicare', 'identifier': '680013229', 'state': 'FL'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'Healthease', 'identifier': 'N196400', 'state': 'FL'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'Staywel Health Plan', 'identifier': 'N196400', 'state': 'FL'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'Wellcare', 'identifier': 'N196400', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NADELL</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2006-06-28</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2008-04-29</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1155412593000</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1600196895000</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1073525747</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '29755 OVERSEAS HWY', 'city': 'BIG PINE KEY', 'state': 'FL', 'postal_code': '330433370', 'telephone_number': '305-872-3735', 'fax_number': '305-872-4792'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '29755 OVERSEAS HWY', 'city': 'BIG PINE KEY', 'state': 'FL', 'postal_code': '330433370', 'telephone_number': '305-872-3735', 'fax_number': '305-872-4792'}]</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>[{'code': '207Q00000X', 'taxonomy_group': '', 'desc': 'Family Medicine', 'state': 'FL', 'license': 'OS 6640', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>[{'endpointType': 'DIRECT', 'endpointTypeDescription': 'Direct Messaging Address', 'endpoint': 'pasquale.dellapi.1@4692.direct.athenahealth.com', 'endpointDescription': 'AMR direct address', 'affiliation': 'N', 'useDescription': '', 'contentTypeDescription': '', 'country_code': 'US', 'country_name': 'United States', 'address_type': 'DOM', 'address_1': '29755 Overseas Hwy', 'city': 'Big Pine Key', 'state': 'FL', 'postal_code': '330433370'}]</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>PASQUALE</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>DELL'API</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>D.O.</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2006-08-12</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2020-09-15</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2020-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1169213979000</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1289496466000</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1386797975</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '3105 INNOVATION DRIVE', 'city': 'ST. CLOUD', 'state': 'FL', 'postal_code': '34769', 'telephone_number': '407-498-0539', 'fax_number': '877-203-2038'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '3105 INNOVATION DRIVE', 'city': 'ST. CLOUD', 'state': 'FL', 'postal_code': '34769', 'telephone_number': '407-498-0539', 'fax_number': '877-203-2038'}]</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>[{'code': '225100000X', 'taxonomy_group': '', 'desc': 'Physical Therapist', 'state': None, 'license': None, 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>JULIUSCAESAR</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>LICONG</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>ORIAS</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Physical Therapist</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2007-01-19</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2010-11-11</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Mr.</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1147131755000</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1760725359000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1104875178</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '330 SW 27TH AVE', 'address_2': 'SUITE 302', 'city': 'MIAMI', 'state': 'FL', 'postal_code': '331352961', 'telephone_number': '305-631-1220', 'fax_number': '305-631-1251'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '330 SW 27TH AVE', 'address_2': 'SUITE 302', 'city': 'MIAMI', 'state': 'FL', 'postal_code': '331352961', 'telephone_number': '305-631-1220', 'fax_number': '305-631-1251'}]</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>[{'code': '208D00000X', 'taxonomy_group': '', 'desc': 'General Practice', 'state': 'FL', 'license': 'ME62522', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>[{'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'BCBS OF FL', 'identifier': '15286', 'state': 'FL'}, {'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '370697400', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>MARIANELA</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>DE LA PORTILLA</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2006-05-08</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1121345863000</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1745324818000</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1558369314</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '221 NE PARK ST', 'city': 'OKEECHOBEE', 'state': 'FL', 'postal_code': '349722923', 'telephone_number': '863-484-6020', 'fax_number': '863-484-6017'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '221 NE PARK ST', 'city': 'OKEECHOBEE', 'state': 'FL', 'postal_code': '349722923', 'telephone_number': '863-484-6020', 'fax_number': '863-462-6017'}]</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '1401 N LAWNWOOD CIR', 'city': 'FORT PIERCE', 'state': 'FL', 'postal_code': '349504835', 'telephone_number': '772-429-3108', 'fax_number': '772-465-0163'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '1124 S PARROTT AVE', 'city': 'OKEECHOBEE', 'state': 'FL', 'postal_code': '349745270', 'telephone_number': '863-484-6020', 'fax_number': '863-484-6017'}]</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>[{'code': '363LX0001X', 'taxonomy_group': '', 'desc': 'Nurse Practitioner, Obstetrics &amp; Gynecology', 'state': 'FL', 'license': 'ARNP2835832', 'primary': False}, {'code': '363LF0000X', 'taxonomy_group': '', 'desc': 'Nurse Practitioner, Family', 'state': 'FL', 'license': 'APRN2835832', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '271798100', 'state': 'FL'}]</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>TAMMY</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>HEDRICK</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>THERESA</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>A.R.N.P.</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2005-07-14</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Mrs.</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1244738455000</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1745948142000</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1851528335</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '555 E CHEVES ST', 'city': 'FLORENCE', 'state': 'SC', 'postal_code': '295062617', 'telephone_number': '843-777-2000'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '1223 COVINA CT', 'city': 'ALLEN', 'state': 'TX', 'postal_code': '750133657', 'telephone_number': '773-412-3916'}]</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>[{'code': '208600000X', 'taxonomy_group': '', 'desc': 'Surgery', 'state': 'IL', 'license': '036167719', 'primary': False}, {'code': '2086S0102X', 'taxonomy_group': '', 'desc': 'Surgery, Surgical Critical Care', 'state': 'SC', 'license': '91104', 'primary': False}, {'code': '2086S0102X', 'taxonomy_group': '', 'desc': 'Surgery, Surgical Critical Care', 'state': 'NC', 'license': '2025-00662', 'primary': False}, {'code': '2086S0102X', 'taxonomy_group': '', 'desc': 'Surgery, Surgical Critical Care', 'state': 'DC', 'license': '210012623', 'primary': False}, {'code': '2086S0102X', 'taxonomy_group': '', 'desc': 'Surgery, Surgical Critical Care', 'state': 'IL', 'license': '036167719', 'primary': False}, {'code': '2086S0102X', 'taxonomy_group': '', 'desc': 'Surgery, Surgical Critical Care', 'state': 'PA', 'license': 'os016264', 'primary': False}, {'code': '2086S0102X', 'taxonomy_group': '193200000X - Multi-Specialty Group', 'desc': 'Surgery, Surgical Critical Care', 'state': 'MO', 'license': '2023015014', 'primary': False}, {'code': '2086S0102X', 'taxonomy_group': '193200000X - Multi-Specialty Group', 'desc': 'Surgery, Surgical Critical Care', 'state': 'IL', 'license': '036.167719', 'primary': False}, {'code': '2086S0127X', 'taxonomy_group': '', 'desc': 'Surgery, Trauma Surgery', 'state': 'IL', 'license': '036167719', 'primary': False}, {'code': '2086S0102X', 'taxonomy_group': '', 'desc': 'Surgery, Surgical Critical Care', 'state': 'TX', 'license': 'Q9616', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '372384301', 'state': 'TX'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'Rail Road Medicare', 'identifier': 'P01844334', 'state': 'TX'}]</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>[{'endpointType': 'DIRECT', 'endpointTypeDescription': 'Direct Messaging Address', 'endpoint': 'egerhardt78392@sih.direct-ci.com', 'affiliation': 'N', 'useDescription': '', 'contentTypeDescription': '', 'country_code': 'US', 'country_name': 'United States', 'address_type': 'DOM', 'address_1': '305 W Jackson St Ste 206', 'city': 'Carbondale', 'state': 'IL', 'postal_code': '629011474'}]</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ERICH</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>GERHARDT</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>PAUL</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>D.O.</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2009-06-11</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1274391720000</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1584980724000</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1568781268</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '290 E MAIN ST STE 200', 'city': 'SMITHTOWN', 'state': 'NY', 'postal_code': '117872916', 'telephone_number': '631-361-5302', 'fax_number': '631-361-8607'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '290 E MAIN ST STE 200', 'city': 'SMITHTOWN', 'state': 'NY', 'postal_code': '117872916', 'telephone_number': '631-361-5302', 'fax_number': '631-361-8607'}]</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>[{'code': '207X00000X', 'taxonomy_group': '', 'desc': 'Orthopaedic Surgery', 'state': 'NY', 'license': '279143', 'primary': False}, {'code': '207X00000X', 'taxonomy_group': '', 'desc': 'Orthopaedic Surgery', 'state': 'TX', 'license': 'Q8255', 'primary': False}, {'code': '207XS0106X', 'taxonomy_group': '', 'desc': 'Orthopaedic Surgery, Hand Surgery', 'state': 'NY', 'license': '279143', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>[{'type': 'Other Name', 'code': '5', 'credential': 'MD', 'first_name': 'FELIPE', 'last_name': 'GUILLEN', 'middle_name': 'TOMAS', 'prefix': 'Dr.', 'suffix': '--'}]</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>PHILLIP</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>GUILLEN</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>TOMAS</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>2010-05-20</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>2020-03-23</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2020-03-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1172524553000</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1585161664000</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1093841728</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '622 W MAPLE ST', 'address_2': 'SUITE C', 'city': 'FARMINGTON', 'state': 'NM', 'postal_code': '874016590', 'telephone_number': '505-327-9694', 'fax_number': '505-327-7524'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '6130 W PARKER RD', 'address_2': 'STE 103', 'city': 'PLANO', 'state': 'TX', 'postal_code': '750937910', 'telephone_number': '505-327-9694', 'fax_number': '505-327-7524'}]</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>[{'code': '208600000X', 'taxonomy_group': '', 'desc': 'Surgery', 'state': 'NM', 'license': '81-114NM', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '21766', 'state': 'NM'}]</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>DENNIS</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>ROBISON</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>M.D.</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2007-02-26</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>2020-03-25</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2020-03-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1277936239000</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1756224354000</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1437460854</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '301 UNIVERSITY BLVD', 'city': 'GALVESTON', 'state': 'TX', 'postal_code': '775559196', 'telephone_number': '409-772-2222'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': 'PO BOX 650859', 'address_2': 'DEPT 710', 'city': 'DALLAS', 'state': 'TX', 'postal_code': '752650859', 'telephone_number': '409-772-2222'}]</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>[{'code': '207XX0801X', 'taxonomy_group': '', 'desc': 'Orthopaedic Surgery, Orthopaedic Trauma', 'state': 'TX', 'license': 'R2862', 'primary': True}, {'code': '207X00000X', 'taxonomy_group': '', 'desc': 'Orthopaedic Surgery', 'state': 'TX', 'license': 'R2862', 'primary': False}]</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>JOHN</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>HAGEDORN</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>CHRISTIAN</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1303673142000</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1484963000000</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1790076826</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '3150 MATLOCK RD STE 401', 'address_2': 'MEDICAL CENTER OF ARLINGTON', 'city': 'ARLINGTON', 'state': 'TX', 'postal_code': '760152924', 'telephone_number': '817-375-9790'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '2925 5TH AVE', 'city': 'FORT WORTH', 'state': 'TX', 'postal_code': '761103428', 'telephone_number': '972-890-2884'}]</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>[{'code': '390200000X', 'taxonomy_group': '', 'desc': 'Student in an Organized Health Care Education/Training Program', 'state': None, 'license': None, 'primary': False}, {'code': '208600000X', 'taxonomy_group': '', 'desc': 'Surgery', 'state': 'TX', 'license': 'q9835', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>ELISABETH</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>JONES BROWN</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>GRACE</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>M.D.</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>2011-04-24</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>2017-01-20</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1244722893000</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1473357141000</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1790912228</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '8042 WURZBACH RD', 'address_2': 'STE 310', 'city': 'SAN ANTONIO', 'state': 'TX', 'postal_code': '782293818', 'telephone_number': '210-614-5113'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '8042 WURZBACH RD', 'address_2': 'STE 310', 'city': 'SAN ANTONIO', 'state': 'TX', 'postal_code': '782293818', 'telephone_number': '210-614-5113'}]</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>[{'code': '208600000X', 'taxonomy_group': '', 'desc': 'Surgery', 'state': 'TX', 'license': 'Q8907', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>TRAVIS</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>HOLLOWAY</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>LAWS</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>M.D.</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>2009-06-11</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>2016-09-08</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1309983663000</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1494427090000</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1710274147</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '5303 HARRY HINES BLVD', 'address_2': '6TH FLOOR', 'city': 'DALLAS', 'state': 'TX', 'postal_code': '753908810', 'telephone_number': '214-645-2225', 'fax_number': '214-645-8451'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': 'PO BOX 845347', 'city': 'DALLAS', 'state': 'TX', 'postal_code': '752843203', 'telephone_number': '214-546-0624', 'fax_number': '214-645-0078'}]</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>[{'code': '207XS0117X', 'taxonomy_group': '', 'desc': 'Orthopaedic Surgery, Orthopaedic Surgery of the Spine', 'state': 'TX', 'license': 'q9068', 'primary': True}, {'code': '207X00000X', 'taxonomy_group': '', 'desc': 'Orthopaedic Surgery', 'state': 'PA', 'license': '198983', 'primary': False}]</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>MICHAEL</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>VAN HAL</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>M.D.</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2011-07-06</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>2017-05-10</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1226682875000</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1521292439000</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1003060211</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '3400 W WHEATLAND RD BLDG 3 # 360', 'city': 'DALLAS', 'state': 'TX', 'postal_code': '75237', 'telephone_number': '214-884-4700', 'fax_number': '214-884-4761'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '1411 N. BECKLEY AVE.', 'address_2': 'PAVILION III, SUITE 268', 'city': 'DALLAS', 'state': 'TX', 'postal_code': '752037520', 'telephone_number': '214-947-4400', 'fax_number': '214-947-4404'}]</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '1265 UNION AVE', 'address_2': 'SUITE 184', 'city': 'MEMPHIS', 'state': 'TN', 'postal_code': '381043415', 'telephone_number': '901-516-9183', 'fax_number': '901-516-8993'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '1265 UNION AVE', 'address_2': 'SUITE 184', 'city': 'MEMPHIS', 'state': 'TN', 'postal_code': '381043415', 'telephone_number': '901-516-9183', 'fax_number': '901-516-8993'}]</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>[{'code': '204F00000X', 'taxonomy_group': '', 'desc': 'Transplant Surgery', 'state': 'TX', 'license': 'R1109', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '03977069', 'state': 'MS'}, {'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '201068001', 'state': 'AR'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'BCBS', 'identifier': '6002233', 'state': 'TN'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'Railroad Medicare', 'identifier': 'P01473968', 'state': 'TN'}, {'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': 'Q002437', 'state': 'TN'}]</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>VICHIN</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>PURI</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>M.D.</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2008-11-14</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>2018-03-17</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1244071530000</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1473865938000</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1669608659</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '126 MEDICAL DR', 'city': 'PALESTINE', 'state': 'TX', 'postal_code': '758018506', 'telephone_number': '903-731-0509', 'fax_number': '903-723-3064'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '126 MEDICAL DR', 'city': 'PALESTINE', 'state': 'TX', 'postal_code': '758018506', 'telephone_number': '903-731-0509', 'fax_number': '903-723-3064'}]</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>[{'code': '208600000X', 'taxonomy_group': '', 'desc': 'Surgery', 'state': 'TX', 'license': 'BP1-0034819', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>RO-JON</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>GROGANS</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>ALLEN</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>M.D.</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2009-06-03</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>2016-09-14</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1269879205000</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1484266240000</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1922323443</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '10815 RR 2222 BLDG 3C', 'address_2': 'STE. 101', 'city': 'AUSTIN', 'state': 'TX', 'postal_code': '787301159', 'telephone_number': '512-717-9475', 'fax_number': '512-498-7535'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': '10815 RR 2222 BLDG 3C', 'address_2': 'STE. 101', 'city': 'AUSTIN', 'state': 'TX', 'postal_code': '787301159', 'telephone_number': '512-717-9475', 'fax_number': '512-498-7535'}]</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>[{'code': '2082S0099X', 'taxonomy_group': '', 'desc': 'Plastic Surgery, Plastic Surgery Within the Head and Neck', 'state': 'TX', 'license': 'Q7457', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>ERIC</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>ROSENBERGER</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>SCOTT</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>2010-03-29</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>2017-01-12</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1256037553000</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>NPI-1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1691610961000</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1508192923</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>[{'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'LOCATION', 'address_type': 'DOM', 'address_1': '430 PENNSYLVANIA AVE STE 350', 'city': 'GLEN ELLYN', 'state': 'IL', 'postal_code': '601374464', 'telephone_number': '630-790-1700', 'fax_number': '630-545-7531'}, {'country_code': 'US', 'country_name': 'United States', 'address_purpose': 'MAILING', 'address_type': 'DOM', 'address_1': 'PO BOX 713260', 'city': 'CHICAGO', 'state': 'IL', 'postal_code': '606771260', 'telephone_number': '630-469-9200'}]</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>[{'code': '208600000X', 'taxonomy_group': '', 'desc': 'Surgery', 'state': 'TX', 'license': 'R0892', 'primary': False}, {'code': '390200000X', 'taxonomy_group': '', 'desc': 'Student in an Organized Health Care Education/Training Program', 'state': None, 'license': None, 'primary': False}, {'code': '208600000X', 'taxonomy_group': '', 'desc': 'Surgery', 'state': 'IL', 'license': '036145913', 'primary': True}]</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>[{'code': '05', 'desc': 'MEDICAID', 'issuer': None, 'identifier': '368074601', 'state': 'TX'}, {'code': '01', 'desc': 'Other (non-Medicare)', 'issuer': 'Blue Cross Blue Shield', 'identifier': '8GL598', 'state': 'TX'}]</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>[{'endpointType': 'DIRECT', 'endpointTypeDescription': 'Direct Messaging Address', 'endpoint': 'jkudsi181195@direct.edward.org', 'affiliation': 'N', 'useDescription': '', 'contentTypeDescription': '', 'country_code': 'US', 'country_name': 'United States', 'address_type': 'DOM', 'address_1': '430 Pennsylvania Ave Ste 350', 'city': 'Glen Ellyn', 'state': 'IL', 'postal_code': '601374464'}]</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>JIHAD</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>KUDSI</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>2009-10-20</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>2023-08-09</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2023-08-09</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
